--- a/Resources/WeaponsStats.xlsx
+++ b/Resources/WeaponsStats.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="105" windowWidth="28695" windowHeight="12540" tabRatio="807" activeTab="6"/>
+    <workbookView xWindow="120" yWindow="105" windowWidth="28695" windowHeight="12540" tabRatio="807" activeTab="13"/>
   </bookViews>
   <sheets>
     <sheet name="Handgun" sheetId="8" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1569" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1572" uniqueCount="522">
   <si>
     <t>Weapon Stats - Sleepy's Weapons</t>
   </si>
@@ -1020,9 +1020,6 @@
     <t>M60E6</t>
   </si>
   <si>
-    <t>M240LW</t>
-  </si>
-  <si>
     <t>M1 GARAND</t>
   </si>
   <si>
@@ -1597,6 +1594,9 @@
   </si>
   <si>
     <t>Colt Python*</t>
+  </si>
+  <si>
+    <t>M240B</t>
   </si>
 </sst>
 </file>
@@ -5955,7 +5955,7 @@
         <v>70</v>
       </c>
       <c r="I1" s="91" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="J1" s="91"/>
       <c r="K1" s="91"/>
@@ -6057,10 +6057,10 @@
         <v>196</v>
       </c>
       <c r="X3" s="17" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Y3" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:25" ht="15.75" thickTop="1">
@@ -6139,10 +6139,10 @@
         <v>124.559568</v>
       </c>
       <c r="X4" s="43" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="Y4" s="43" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -6221,10 +6221,10 @@
         <v>98.30543333333334</v>
       </c>
       <c r="X5" s="43" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Y5" s="43" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -6303,10 +6303,10 @@
         <v>137.08577142857141</v>
       </c>
       <c r="X6" s="43" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Y6" s="43" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -6385,10 +6385,10 @@
         <v>136.71688101265821</v>
       </c>
       <c r="X7" s="43" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Y7" s="43" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -6467,10 +6467,10 @@
         <v>140.02148837209302</v>
       </c>
       <c r="X8" s="43" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Y8" s="43" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -6549,10 +6549,10 @@
         <v>121.32425454545456</v>
       </c>
       <c r="X9" s="43" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Y9" s="43" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -6631,10 +6631,10 @@
         <v>122.36704615384613</v>
       </c>
       <c r="X10" s="43" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Y10" s="43" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -6714,10 +6714,10 @@
         <v>122.36894366197183</v>
       </c>
       <c r="X11" s="43" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Y11" s="43" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -6796,10 +6796,10 @@
         <v>130.12782857142858</v>
       </c>
       <c r="X12" s="43" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Y12" s="43" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -6878,10 +6878,10 @@
         <v>132.70607999999999</v>
       </c>
       <c r="X13" s="43" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Y13" s="43" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="14" spans="1:25" s="4" customFormat="1">
@@ -6960,10 +6960,10 @@
         <v>136.58674615384615</v>
       </c>
       <c r="X14" s="43" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Y14" s="43" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -7042,10 +7042,10 @@
         <v>125.33352000000002</v>
       </c>
       <c r="X15" s="43" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Y15" s="43" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -7124,10 +7124,10 @@
         <v>92.734384615384613</v>
       </c>
       <c r="X16" s="43" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Y16" s="43" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -7206,10 +7206,10 @@
         <v>93.495969863013684</v>
       </c>
       <c r="X17" s="43" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Y17" s="43" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -7288,10 +7288,10 @@
         <v>106.94154545454545</v>
       </c>
       <c r="X18" s="43" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Y18" s="43" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -7370,10 +7370,10 @@
         <v>123.72722123893799</v>
       </c>
       <c r="X19" s="43" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="Y19" s="43" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -7452,10 +7452,10 @@
         <v>124.89113739130434</v>
       </c>
       <c r="X20" s="43" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="Y20" s="43" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -7534,10 +7534,10 @@
         <v>158.93301492537313</v>
       </c>
       <c r="X21" s="43" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Y21" s="43" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -7616,10 +7616,10 @@
         <v>109.69452307692309</v>
       </c>
       <c r="X22" s="43" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Y22" s="43" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -7698,10 +7698,10 @@
         <v>125.71587692307689</v>
       </c>
       <c r="X23" s="43" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Y23" s="43" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -7780,15 +7780,15 @@
         <v>134.56470857142855</v>
       </c>
       <c r="X24" s="43" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Y24" s="43" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="25" spans="1:25">
       <c r="A25" s="92" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B25" s="4">
         <v>4</v>
@@ -7862,10 +7862,10 @@
         <v>142.29993513513509</v>
       </c>
       <c r="X25" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="Y25" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="26" spans="1:25" s="72" customFormat="1">
@@ -8755,7 +8755,7 @@
         <v>68</v>
       </c>
       <c r="I1" s="91" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="J1" s="91"/>
       <c r="K1" s="91"/>
@@ -8858,10 +8858,10 @@
         <v>196</v>
       </c>
       <c r="X3" s="17" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Y3" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:25" ht="15.75" thickTop="1">
@@ -8940,10 +8940,10 @@
         <v>245.12130000000002</v>
       </c>
       <c r="X4" s="49" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="Y4" s="49" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -9022,15 +9022,15 @@
         <v>207.29664</v>
       </c>
       <c r="X5" s="49" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="Y5" s="49" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="6" spans="1:25">
       <c r="A6" s="49" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B6" s="56">
         <v>2</v>
@@ -9104,10 +9104,10 @@
         <v>250.29575999999997</v>
       </c>
       <c r="X6" s="49" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="Y6" s="49" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -9186,15 +9186,15 @@
         <v>262.80879545454542</v>
       </c>
       <c r="X7" s="49" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y7" s="49" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="8" spans="1:25">
       <c r="A8" s="49" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B8" s="56">
         <v>4</v>
@@ -9268,15 +9268,15 @@
         <v>272.7619578947369</v>
       </c>
       <c r="X8" s="49" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y8" s="49" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="9" spans="1:25" s="72" customFormat="1">
       <c r="A9" s="56" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B9" s="66">
         <v>4</v>
@@ -9350,15 +9350,15 @@
         <v>255.47912432432432</v>
       </c>
       <c r="X9" s="49" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y9" s="49" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="10" spans="1:25">
       <c r="A10" s="56" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B10" s="56">
         <v>4</v>
@@ -9432,10 +9432,10 @@
         <v>231.31559999999999</v>
       </c>
       <c r="X10" s="49" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y10" s="49" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -10016,7 +10016,7 @@
         <v>68</v>
       </c>
       <c r="I1" s="91" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="J1" s="91"/>
       <c r="K1" s="91"/>
@@ -10119,10 +10119,10 @@
         <v>196</v>
       </c>
       <c r="X3" s="17" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Y3" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:25" s="72" customFormat="1" ht="15.75" thickTop="1">
@@ -10202,10 +10202,10 @@
         <v>375.19815041379303</v>
       </c>
       <c r="X4" s="49" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="Y4" s="49" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -11032,7 +11032,7 @@
         <v>165</v>
       </c>
       <c r="H1" s="91" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="I1" s="91"/>
       <c r="J1" s="91"/>
@@ -11133,10 +11133,10 @@
         <v>196</v>
       </c>
       <c r="X3" s="17" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Y3" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:25" s="72" customFormat="1" ht="15.75" thickTop="1">
@@ -12124,10 +12124,10 @@
         <v>247</v>
       </c>
       <c r="AG3" s="17" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AH3" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AI3" t="s">
         <v>100</v>
@@ -12234,10 +12234,10 @@
         <v>0</v>
       </c>
       <c r="AF4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AI4" s="12" t="s">
         <v>103</v>
@@ -12344,10 +12344,10 @@
         <v>0</v>
       </c>
       <c r="AF5" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AI5" s="12" t="s">
         <v>103</v>
@@ -12455,7 +12455,7 @@
         <v>0</v>
       </c>
       <c r="AF6" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AI6" s="12" t="s">
         <v>103</v>
@@ -12562,7 +12562,7 @@
         <v>0</v>
       </c>
       <c r="AF7" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AI7" s="12" t="s">
         <v>103</v>
@@ -12668,7 +12668,7 @@
         <v>0</v>
       </c>
       <c r="AF8" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG8" s="4"/>
       <c r="AH8" s="4"/>
@@ -12681,7 +12681,7 @@
     </row>
     <row r="9" spans="1:36">
       <c r="A9" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B9" s="35" t="s">
         <v>288</v>
@@ -12777,7 +12777,7 @@
         <v>0</v>
       </c>
       <c r="AF9" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AI9" s="12" t="s">
         <v>103</v>
@@ -12788,7 +12788,7 @@
     </row>
     <row r="10" spans="1:36">
       <c r="A10" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B10" s="35" t="s">
         <v>288</v>
@@ -12875,7 +12875,7 @@
         <v>0.22222222222222221</v>
       </c>
       <c r="AC10" s="46" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AD10" s="46" t="s">
         <v>87</v>
@@ -12884,7 +12884,7 @@
         <v>0</v>
       </c>
       <c r="AF10" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AI10" s="12" t="s">
         <v>103</v>
@@ -12895,7 +12895,7 @@
     </row>
     <row r="11" spans="1:36">
       <c r="A11" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B11" s="35" t="s">
         <v>288</v>
@@ -12991,7 +12991,7 @@
         <v>0</v>
       </c>
       <c r="AF11" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AI11" s="12" t="s">
         <v>103</v>
@@ -13002,7 +13002,7 @@
     </row>
     <row r="12" spans="1:36">
       <c r="A12" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B12" s="35" t="s">
         <v>288</v>
@@ -13097,7 +13097,7 @@
         <v>0</v>
       </c>
       <c r="AF12" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AI12" s="12" t="s">
         <v>103</v>
@@ -13108,7 +13108,7 @@
     </row>
     <row r="13" spans="1:36">
       <c r="A13" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B13" s="35" t="s">
         <v>288</v>
@@ -13203,7 +13203,7 @@
         <v>0</v>
       </c>
       <c r="AF13" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AI13" s="12">
         <v>1.9</v>
@@ -13214,7 +13214,7 @@
     </row>
     <row r="14" spans="1:36">
       <c r="A14" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B14" s="35" t="s">
         <v>288</v>
@@ -13309,7 +13309,7 @@
         <v>0</v>
       </c>
       <c r="AF14" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AI14" s="13">
         <v>2.9</v>
@@ -13320,7 +13320,7 @@
     </row>
     <row r="15" spans="1:36">
       <c r="A15" s="7" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B15" s="35" t="s">
         <v>288</v>
@@ -13416,7 +13416,7 @@
         <v>0</v>
       </c>
       <c r="AF15" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AI15" s="12">
         <v>3.9</v>
@@ -13427,7 +13427,7 @@
     </row>
     <row r="16" spans="1:36">
       <c r="A16" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B16" s="35" t="s">
         <v>288</v>
@@ -13522,7 +13522,7 @@
         <v>0</v>
       </c>
       <c r="AF16" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AI16" s="12">
         <v>4.9000000000000004</v>
@@ -13533,7 +13533,7 @@
     </row>
     <row r="17" spans="1:36">
       <c r="A17" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B17" s="35" t="s">
         <v>288</v>
@@ -13628,7 +13628,7 @@
         <v>0</v>
       </c>
       <c r="AF17" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AI17" s="12">
         <v>5.9</v>
@@ -13639,7 +13639,7 @@
     </row>
     <row r="18" spans="1:36">
       <c r="A18" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B18" s="35" t="s">
         <v>288</v>
@@ -13734,7 +13734,7 @@
         <v>0</v>
       </c>
       <c r="AF18" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AI18" s="96">
         <v>7.9</v>
@@ -13844,7 +13844,7 @@
         <v>-150</v>
       </c>
       <c r="AF19" s="72" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG19" s="72"/>
       <c r="AH19" s="72"/>
@@ -13952,7 +13952,7 @@
         <v>-80</v>
       </c>
       <c r="AF20" s="72" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG20" s="72"/>
       <c r="AH20" s="72"/>
@@ -14059,7 +14059,7 @@
         <v>-150</v>
       </c>
       <c r="AF21" s="72" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG21" s="72"/>
       <c r="AH21" s="72"/>
@@ -14068,7 +14068,7 @@
     </row>
     <row r="22" spans="1:36">
       <c r="A22" s="14" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>288</v>
@@ -14164,10 +14164,10 @@
         <v>-100</v>
       </c>
       <c r="AF22" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG22" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AI22" s="12" t="s">
         <v>103</v>
@@ -14178,7 +14178,7 @@
     </row>
     <row r="23" spans="1:36">
       <c r="A23" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B23" s="35" t="s">
         <v>288</v>
@@ -14274,10 +14274,10 @@
         <v>-100</v>
       </c>
       <c r="AF23" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG23" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AI23" s="12" t="s">
         <v>103</v>
@@ -14288,7 +14288,7 @@
     </row>
     <row r="24" spans="1:36">
       <c r="A24" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B24" s="35" t="s">
         <v>288</v>
@@ -14384,10 +14384,10 @@
         <v>-200</v>
       </c>
       <c r="AF24" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG24" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AI24" s="12" t="s">
         <v>103</v>
@@ -14493,7 +14493,7 @@
         <v>-200</v>
       </c>
       <c r="AF25" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG25"/>
       <c r="AH25"/>
@@ -14506,7 +14506,7 @@
     </row>
     <row r="26" spans="1:36">
       <c r="A26" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B26" s="35" t="s">
         <v>288</v>
@@ -14600,7 +14600,7 @@
         <v>0</v>
       </c>
       <c r="AF26" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AI26" s="12" t="s">
         <v>103</v>
@@ -14611,7 +14611,7 @@
     </row>
     <row r="27" spans="1:36">
       <c r="A27" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B27" s="35" t="s">
         <v>288</v>
@@ -14698,7 +14698,7 @@
         <v>0.6</v>
       </c>
       <c r="AC27" s="46" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AD27" s="46" t="s">
         <v>87</v>
@@ -14707,7 +14707,7 @@
         <v>-150</v>
       </c>
       <c r="AF27" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AI27" s="12" t="s">
         <v>103</v>
@@ -14718,7 +14718,7 @@
     </row>
     <row r="28" spans="1:36" s="95" customFormat="1">
       <c r="A28" s="7" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B28" s="35" t="s">
         <v>288</v>
@@ -14806,7 +14806,7 @@
       </c>
       <c r="AB28" s="7"/>
       <c r="AC28" s="46" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AD28" s="54" t="s">
         <v>87</v>
@@ -14815,7 +14815,7 @@
         <v>-200</v>
       </c>
       <c r="AF28" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG28" s="53"/>
       <c r="AH28" s="53"/>
@@ -14828,7 +14828,7 @@
     </row>
     <row r="29" spans="1:36">
       <c r="A29" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B29" s="35" t="s">
         <v>288</v>
@@ -14924,7 +14924,7 @@
         <v>-200</v>
       </c>
       <c r="AF29" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AI29" s="12" t="s">
         <v>103</v>
@@ -14935,7 +14935,7 @@
     </row>
     <row r="30" spans="1:36">
       <c r="A30" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B30" s="35" t="s">
         <v>288</v>
@@ -15031,7 +15031,7 @@
         <v>-200</v>
       </c>
       <c r="AF30" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AI30" s="12" t="s">
         <v>103</v>
@@ -15042,7 +15042,7 @@
     </row>
     <row r="31" spans="1:36">
       <c r="A31" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B31" s="35" t="s">
         <v>288</v>
@@ -15137,7 +15137,7 @@
         <v>-250</v>
       </c>
       <c r="AF31" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AI31" s="12" t="s">
         <v>103</v>
@@ -15148,7 +15148,7 @@
     </row>
     <row r="32" spans="1:36">
       <c r="A32" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B32" s="35" t="s">
         <v>288</v>
@@ -15243,7 +15243,7 @@
         <v>-300</v>
       </c>
       <c r="AF32" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AI32" s="12">
         <v>1.9</v>
@@ -15254,7 +15254,7 @@
     </row>
     <row r="33" spans="1:36">
       <c r="A33" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B33" s="35" t="s">
         <v>288</v>
@@ -15346,7 +15346,7 @@
         <v>-350</v>
       </c>
       <c r="AF33" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AI33" s="12">
         <v>3.9</v>
@@ -15357,7 +15357,7 @@
     </row>
     <row r="34" spans="1:36">
       <c r="A34" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B34" s="35" t="s">
         <v>288</v>
@@ -15452,7 +15452,7 @@
         <v>0</v>
       </c>
       <c r="AF34" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AI34" s="12" t="s">
         <v>103</v>
@@ -15979,7 +15979,7 @@
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="91" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1" s="91"/>
       <c r="I1" s="91"/>
@@ -16045,16 +16045,16 @@
         <v>204</v>
       </c>
       <c r="R3" s="17" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="S3" s="17" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="T3" s="17" t="s">
+        <v>340</v>
+      </c>
+      <c r="U3" s="17" t="s">
         <v>341</v>
-      </c>
-      <c r="U3" s="17" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:21" s="4" customFormat="1" ht="15.75" thickTop="1">
@@ -16109,13 +16109,13 @@
       <c r="Q4" s="30"/>
       <c r="R4" s="30"/>
       <c r="S4" s="30" t="s">
+        <v>400</v>
+      </c>
+      <c r="T4" s="68" t="s">
         <v>401</v>
       </c>
-      <c r="T4" s="68" t="s">
-        <v>402</v>
-      </c>
       <c r="U4" s="30" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="5" spans="1:21">
@@ -16170,13 +16170,13 @@
       <c r="Q5" s="30"/>
       <c r="R5" s="30"/>
       <c r="S5" s="30" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="T5" s="68" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="U5" s="30" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -16231,13 +16231,13 @@
       <c r="Q6" s="30"/>
       <c r="R6" s="30"/>
       <c r="S6" s="30" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="T6" s="68" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="U6" s="30" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="7" spans="1:21">
@@ -16292,13 +16292,13 @@
       <c r="Q7" s="30"/>
       <c r="R7" s="30"/>
       <c r="S7" s="68" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="T7" s="69" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="U7" s="30" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="8" spans="1:21">
@@ -16353,10 +16353,10 @@
       <c r="Q8" s="30"/>
       <c r="R8" s="30"/>
       <c r="S8" s="68" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="T8" s="68" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="U8" s="30"/>
     </row>
@@ -16412,13 +16412,13 @@
       <c r="Q9" s="30"/>
       <c r="R9" s="30"/>
       <c r="S9" s="30" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="T9" s="68" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="U9" s="30" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="10" spans="1:21">
@@ -16477,7 +16477,7 @@
       <c r="S10" s="30"/>
       <c r="T10" s="68"/>
       <c r="U10" s="30" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -16532,13 +16532,13 @@
       <c r="Q11" s="30"/>
       <c r="R11" s="30"/>
       <c r="S11" s="30" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="T11" s="68" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="U11" s="30" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="12" spans="1:21">
@@ -16593,13 +16593,13 @@
       <c r="Q12" s="30"/>
       <c r="R12" s="30"/>
       <c r="S12" s="30" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="T12" s="68" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="U12" s="30" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="13" spans="1:21">
@@ -16653,19 +16653,19 @@
       </c>
       <c r="Q13" s="33"/>
       <c r="R13" s="33"/>
-      <c r="S13" s="33" t="s">
-        <v>373</v>
+      <c r="S13" s="30" t="s">
+        <v>372</v>
       </c>
       <c r="T13" s="68" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="U13" s="33" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="14" spans="1:21" s="4" customFormat="1">
       <c r="A14" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B14" s="10">
         <v>4</v>
@@ -16715,13 +16715,13 @@
       <c r="Q14" s="33"/>
       <c r="R14" s="33"/>
       <c r="S14" s="30" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="T14" s="68" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="U14" s="30" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="15" spans="1:21">
@@ -16775,21 +16775,21 @@
       </c>
       <c r="Q15" s="27"/>
       <c r="R15" s="27" t="s">
+        <v>370</v>
+      </c>
+      <c r="S15" s="27" t="s">
+        <v>369</v>
+      </c>
+      <c r="T15" s="68" t="s">
+        <v>345</v>
+      </c>
+      <c r="U15" s="27" t="s">
         <v>371</v>
-      </c>
-      <c r="S15" s="27" t="s">
-        <v>370</v>
-      </c>
-      <c r="T15" s="68" t="s">
-        <v>346</v>
-      </c>
-      <c r="U15" s="27" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="16" spans="1:21">
       <c r="A16" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B16">
         <v>4</v>
@@ -16838,9 +16838,15 @@
       </c>
       <c r="Q16" s="41"/>
       <c r="R16" s="41"/>
-      <c r="S16" s="41"/>
-      <c r="T16" s="69"/>
-      <c r="U16" s="41"/>
+      <c r="S16" s="30" t="s">
+        <v>372</v>
+      </c>
+      <c r="T16" s="68" t="s">
+        <v>339</v>
+      </c>
+      <c r="U16" s="33" t="s">
+        <v>342</v>
+      </c>
     </row>
     <row r="17" spans="1:21">
       <c r="A17" s="6" t="s">
@@ -17009,7 +17015,7 @@
     </row>
     <row r="20" spans="1:21">
       <c r="A20" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B20" s="4">
         <v>5</v>
@@ -17059,13 +17065,13 @@
       <c r="Q20" s="30"/>
       <c r="R20" s="30"/>
       <c r="S20" s="30" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="T20" s="68" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="U20" s="30" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -17747,12 +17753,12 @@
         <v>24</v>
       </c>
       <c r="F1" s="91" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G1" s="91"/>
       <c r="H1" s="91"/>
       <c r="V1" s="35" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="W1">
         <v>250</v>
@@ -17862,10 +17868,10 @@
         <v>247</v>
       </c>
       <c r="AA3" s="17" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AB3" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:28">
@@ -18134,13 +18140,13 @@
         <v>255</v>
       </c>
       <c r="G1" t="s">
+        <v>518</v>
+      </c>
+      <c r="H1" t="s">
+        <v>517</v>
+      </c>
+      <c r="I1" t="s">
         <v>519</v>
-      </c>
-      <c r="H1" t="s">
-        <v>518</v>
-      </c>
-      <c r="I1" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -18671,7 +18677,7 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B15">
         <f>COUNTIF(Spare!B:B, 1)</f>
@@ -18824,7 +18830,7 @@
       </c>
       <c r="B25" s="1"/>
       <c r="D25" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -18847,10 +18853,10 @@
         <v>4.3478260869565224</v>
       </c>
       <c r="D27" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E27" t="s">
         <v>448</v>
-      </c>
-      <c r="E27" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="28" spans="1:18">
@@ -18862,10 +18868,10 @@
         <v>4.545454545454545</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E28" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="29" spans="1:18">
@@ -18877,10 +18883,10 @@
         <v>4.7619047619047619</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E29" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -18892,10 +18898,10 @@
         <v>5.25</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E30" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="31" spans="1:18">
@@ -50240,7 +50246,7 @@
         <v>69</v>
       </c>
       <c r="I1" s="91" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="J1" s="91"/>
       <c r="K1" s="91"/>
@@ -50342,15 +50348,15 @@
         <v>196</v>
       </c>
       <c r="X3" s="17" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Y3" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:25">
       <c r="A4" s="4" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B4" s="12">
         <v>4</v>
@@ -50424,10 +50430,10 @@
         <v>133.68375</v>
       </c>
       <c r="X4" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="Y4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -50506,10 +50512,10 @@
         <v>136.94803977272727</v>
       </c>
       <c r="X5" t="s">
+        <v>488</v>
+      </c>
+      <c r="Y5" t="s">
         <v>489</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -50588,10 +50594,10 @@
         <v>143.62701923076924</v>
       </c>
       <c r="X6" t="s">
+        <v>488</v>
+      </c>
+      <c r="Y6" t="s">
         <v>489</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -50670,10 +50676,10 @@
         <v>128.82354294478526</v>
       </c>
       <c r="X7" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="Y7" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="8" spans="1:25" s="72" customFormat="1">
@@ -51246,7 +51252,7 @@
         <v>77</v>
       </c>
       <c r="H1" s="91" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="I1" s="91"/>
       <c r="J1" s="91"/>
@@ -51349,10 +51355,10 @@
         <v>196</v>
       </c>
       <c r="X3" s="17" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Y3" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -51432,10 +51438,10 @@
         <v>234.51120000000003</v>
       </c>
       <c r="X4" s="47" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Y4" s="47" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -51515,10 +51521,10 @@
         <v>235.18637619961612</v>
       </c>
       <c r="X5" s="47" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Y5" s="47" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -51598,10 +51604,10 @@
         <v>238.48288524590157</v>
       </c>
       <c r="X6" s="47" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Y6" s="47" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -51681,15 +51687,15 @@
         <v>231.73919999999998</v>
       </c>
       <c r="X7" s="47" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Y7" s="47" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="8" spans="1:25">
       <c r="A8" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B8" s="12">
         <v>4</v>
@@ -51763,10 +51769,10 @@
         <v>218.52600000000001</v>
       </c>
       <c r="X8" s="70" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Y8" s="70" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9" spans="1:25" s="72" customFormat="1">
@@ -51853,7 +51859,7 @@
     </row>
     <row r="10" spans="1:25" s="4" customFormat="1">
       <c r="A10" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B10" s="12">
         <v>7</v>
@@ -51928,10 +51934,10 @@
         <v>244.26683544303796</v>
       </c>
       <c r="X10" s="70" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Y10" s="70" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -52730,7 +52736,7 @@
         <v>77</v>
       </c>
       <c r="H1" s="91" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="I1" s="91"/>
       <c r="J1" s="91"/>
@@ -52833,10 +52839,10 @@
         <v>196</v>
       </c>
       <c r="X3" s="17" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Y3" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -52916,10 +52922,10 @@
         <v>312.49496249999999</v>
       </c>
       <c r="X4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Y4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -52999,10 +53005,10 @@
         <v>313.61579999999992</v>
       </c>
       <c r="X5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="Y5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -53082,10 +53088,10 @@
         <v>342.24119999999994</v>
       </c>
       <c r="X6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Y6" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -53164,10 +53170,10 @@
         <v>279.40946478260872</v>
       </c>
       <c r="X7" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="Y7" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -53247,10 +53253,10 @@
         <v>371.11693892617444</v>
       </c>
       <c r="X8" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Y8" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -53330,10 +53336,10 @@
         <v>334.50164999999993</v>
       </c>
       <c r="X9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y9" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="10" spans="1:25" s="4" customFormat="1">
@@ -53413,10 +53419,10 @@
         <v>253.90628731343276</v>
       </c>
       <c r="X10" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Y10" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -53496,10 +53502,10 @@
         <v>296.41466570617388</v>
       </c>
       <c r="X11" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Y11" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -53579,10 +53585,10 @@
         <v>267.0202536585366</v>
       </c>
       <c r="X12" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Y12" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -53662,15 +53668,15 @@
         <v>320.25490714285712</v>
       </c>
       <c r="X13" t="s">
+        <v>492</v>
+      </c>
+      <c r="Y13" t="s">
         <v>493</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="14" spans="1:25">
       <c r="A14" s="92" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B14" s="12">
         <v>4</v>
@@ -53745,15 +53751,15 @@
         <v>305.39954716981123</v>
       </c>
       <c r="X14" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="Y14" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="15" spans="1:25">
       <c r="A15" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B15" s="12">
         <v>4</v>
@@ -53828,15 +53834,15 @@
         <v>284.50660744567688</v>
       </c>
       <c r="X15" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Y15" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="16" spans="1:25" s="72" customFormat="1">
       <c r="A16" s="90" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B16" s="12">
         <v>5</v>
@@ -53911,15 +53917,15 @@
         <v>341.74395169811316</v>
       </c>
       <c r="X16" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="Y16" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="17" spans="1:25">
       <c r="A17" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B17" s="12">
         <v>5</v>
@@ -53994,15 +54000,15 @@
         <v>320.16817642585551</v>
       </c>
       <c r="X17" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="Y17" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="18" spans="1:25">
       <c r="A18" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B18" s="12">
         <v>5</v>
@@ -54077,15 +54083,15 @@
         <v>334.50662686567159</v>
       </c>
       <c r="X18" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="Y18" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="19" spans="1:25">
       <c r="A19" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B19" s="4">
         <v>5</v>
@@ -54160,10 +54166,10 @@
         <v>340.51474285714283</v>
       </c>
       <c r="X19" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="Y19" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -54723,7 +54729,7 @@
         <v>76</v>
       </c>
       <c r="J1" s="91" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="K1" s="91"/>
       <c r="L1" s="91"/>
@@ -54826,10 +54832,10 @@
         <v>196</v>
       </c>
       <c r="X3" s="17" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="Y3" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="Z3" t="s">
         <v>281</v>
@@ -54924,10 +54930,10 @@
         <v>474.93261853714284</v>
       </c>
       <c r="X4" s="36" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="Y4" s="36" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Z4" s="52"/>
       <c r="AA4" s="52"/>
@@ -55012,10 +55018,10 @@
         <v>444.35848720714284</v>
       </c>
       <c r="X5" s="36" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="Y5" s="36" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Z5" s="52"/>
       <c r="AA5" s="52"/>
@@ -55100,10 +55106,10 @@
         <v>498.23036144708402</v>
       </c>
       <c r="X6" s="36" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="Y6" s="36" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Z6" s="52"/>
       <c r="AA6" s="52"/>
@@ -55188,10 +55194,10 @@
         <v>445.79325727192503</v>
       </c>
       <c r="X7" s="36" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="Y7" s="36" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Z7" s="52"/>
       <c r="AA7" s="52"/>
@@ -55276,10 +55282,10 @@
         <v>479.78898065024617</v>
       </c>
       <c r="X8" s="36" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="Y8" s="36" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Z8" s="52"/>
       <c r="AA8" s="52"/>
@@ -55364,10 +55370,10 @@
         <v>507.63802516885562</v>
       </c>
       <c r="X9" s="36" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="Y9" s="36" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Z9" s="52"/>
       <c r="AA9" s="52"/>
@@ -55452,10 +55458,10 @@
         <v>447.1080023835616</v>
       </c>
       <c r="X10" s="36" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="Y10" s="36" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Z10" s="52"/>
       <c r="AA10" s="52"/>
@@ -55540,10 +55546,10 @@
         <v>465.82127712301576</v>
       </c>
       <c r="X11" s="36" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="Y11" s="36" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Z11" s="52"/>
       <c r="AA11" s="52"/>
@@ -55628,10 +55634,10 @@
         <v>451.94825712650595</v>
       </c>
       <c r="X12" s="36" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="Y12" s="36" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Z12" s="52"/>
       <c r="AA12" s="52"/>
@@ -55715,10 +55721,10 @@
         <v>480</v>
       </c>
       <c r="X13" s="36" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Y13" s="36" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Z13" s="35"/>
       <c r="AA13" s="35"/>
@@ -55802,10 +55808,10 @@
         <v>480</v>
       </c>
       <c r="X14" s="36" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Y14" s="36" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Z14" s="35"/>
       <c r="AA14" s="35"/>
@@ -55889,10 +55895,10 @@
         <v>530</v>
       </c>
       <c r="X15" s="36" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Y15" s="36" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Z15" s="35"/>
       <c r="AA15" s="35"/>
@@ -55976,10 +55982,10 @@
         <v>352.69755624999999</v>
       </c>
       <c r="X16" s="36" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="Y16" s="36" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="Z16" s="52"/>
       <c r="AA16" s="52"/>
@@ -56064,10 +56070,10 @@
         <v>367.02486600000003</v>
       </c>
       <c r="X17" s="71" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="Y17" s="71" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Z17" s="52"/>
       <c r="AA17" s="52"/>
@@ -56152,10 +56158,10 @@
         <v>476.81819949438193</v>
       </c>
       <c r="X18" s="36" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="Y18" s="36" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Z18" s="52"/>
       <c r="AA18" s="52"/>
@@ -56239,10 +56245,10 @@
         <v>455</v>
       </c>
       <c r="X19" s="36" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="Y19" s="36" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Z19" s="35"/>
       <c r="AA19" s="35"/>
@@ -56326,10 +56332,10 @@
         <v>460</v>
       </c>
       <c r="X20" s="36" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Y20" s="36" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Z20" s="35"/>
       <c r="AA20" s="35"/>
@@ -56412,10 +56418,10 @@
         <v>410</v>
       </c>
       <c r="X21" s="36" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="Y21" s="36" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="Z21" s="35"/>
       <c r="AA21" s="35"/>
@@ -56499,10 +56505,10 @@
         <v>435</v>
       </c>
       <c r="X22" s="36" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Y22" s="36" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Z22" s="35"/>
       <c r="AA22" s="35"/>
@@ -56587,10 +56593,10 @@
         <v>431.17471603910616</v>
       </c>
       <c r="X23" s="36" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="Y23" s="36" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Z23" s="52"/>
       <c r="AA23" s="52"/>
@@ -56675,10 +56681,10 @@
         <v>450.11722884375001</v>
       </c>
       <c r="X24" s="36" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Y24" s="36" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Z24" s="52"/>
       <c r="AA24" s="52"/>
@@ -56763,10 +56769,10 @@
         <v>473.69235374999994</v>
       </c>
       <c r="X25" s="36" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Y25" s="36" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Z25" s="52"/>
       <c r="AA25" s="52"/>
@@ -56850,10 +56856,10 @@
         <v>650</v>
       </c>
       <c r="X26" s="36" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Y26" s="36" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Z26" s="35" t="s">
         <v>282</v>
@@ -56948,10 +56954,10 @@
         <v>362.75058273924117</v>
       </c>
       <c r="X27" s="36" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Y27" s="36" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Z27" s="52"/>
       <c r="AA27" s="52"/>
@@ -57036,10 +57042,10 @@
         <v>480.56658642323038</v>
       </c>
       <c r="X28" s="36" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="Y28" s="36" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Z28" s="52"/>
       <c r="AA28" s="52"/>
@@ -57124,10 +57130,10 @@
         <v>512.74941366426435</v>
       </c>
       <c r="X29" s="36" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="Y29" s="36" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Z29" s="52"/>
       <c r="AA29" s="52"/>
@@ -57212,10 +57218,10 @@
         <v>403.70850173076923</v>
       </c>
       <c r="X30" s="36" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="Y30" s="36" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Z30" s="52"/>
       <c r="AA30" s="52"/>
@@ -57300,10 +57306,10 @@
         <v>372.14887499999992</v>
       </c>
       <c r="X31" s="36" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Y31" s="36" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Z31" s="52"/>
       <c r="AA31" s="52"/>
@@ -57388,10 +57394,10 @@
         <v>475.96708106557378</v>
       </c>
       <c r="X32" s="36" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Y32" s="36" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Z32" s="52"/>
       <c r="AA32" s="52"/>
@@ -57476,10 +57482,10 @@
         <v>371.25391135135135</v>
       </c>
       <c r="X33" s="36" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="Y33" s="36" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Z33" s="52"/>
       <c r="AA33" s="52"/>
@@ -57489,7 +57495,7 @@
     </row>
     <row r="34" spans="1:30">
       <c r="A34" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B34" s="12">
         <v>4</v>
@@ -57564,10 +57570,10 @@
         <v>437.33909172413792</v>
       </c>
       <c r="X34" s="36" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="Y34" s="36" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Z34" s="35"/>
       <c r="AA34" s="35"/>
@@ -57577,7 +57583,7 @@
     </row>
     <row r="35" spans="1:30">
       <c r="A35" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B35">
         <v>4</v>
@@ -57652,10 +57658,10 @@
         <v>466.90890940054504</v>
       </c>
       <c r="X35" s="36" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Y35" s="36" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Z35" s="52"/>
       <c r="AA35" s="52"/>
@@ -57665,7 +57671,7 @@
     </row>
     <row r="36" spans="1:30">
       <c r="A36" s="14" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B36">
         <v>4</v>
@@ -57740,10 +57746,10 @@
         <v>461.94384610650894</v>
       </c>
       <c r="X36" s="36" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="Y36" s="36" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Z36" s="52"/>
       <c r="AA36" s="52"/>
@@ -57753,7 +57759,7 @@
     </row>
     <row r="37" spans="1:30">
       <c r="A37" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B37">
         <v>4</v>
@@ -57828,10 +57834,10 @@
         <v>413.05800359597913</v>
       </c>
       <c r="X37" s="36" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="Y37" s="36" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Z37" s="35"/>
       <c r="AA37" s="35"/>
@@ -57841,7 +57847,7 @@
     </row>
     <row r="38" spans="1:30">
       <c r="A38" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B38">
         <v>4</v>
@@ -57915,10 +57921,10 @@
         <v>369.1838358</v>
       </c>
       <c r="X38" s="36" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="Y38" s="36" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Z38" s="35"/>
       <c r="AA38" s="35"/>
@@ -57928,7 +57934,7 @@
     </row>
     <row r="39" spans="1:30">
       <c r="A39" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B39">
         <v>4</v>
@@ -58002,10 +58008,10 @@
         <v>381.80020846153849</v>
       </c>
       <c r="X39" s="36" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="Y39" s="36" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Z39" s="35"/>
       <c r="AA39" s="35"/>
@@ -58015,7 +58021,7 @@
     </row>
     <row r="40" spans="1:30">
       <c r="A40" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B40">
         <v>4</v>
@@ -58090,10 +58096,10 @@
         <v>461.7549800173565</v>
       </c>
       <c r="X40" s="36" t="s">
+        <v>499</v>
+      </c>
+      <c r="Y40" s="36" t="s">
         <v>500</v>
-      </c>
-      <c r="Y40" s="36" t="s">
-        <v>501</v>
       </c>
       <c r="Z40" s="35"/>
       <c r="AA40" s="35"/>
@@ -58103,7 +58109,7 @@
     </row>
     <row r="41" spans="1:30" s="72" customFormat="1">
       <c r="A41" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B41">
         <v>4</v>
@@ -58178,10 +58184,10 @@
         <v>499.36223178947364</v>
       </c>
       <c r="X41" s="36" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Y41" s="36" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Z41" s="52"/>
       <c r="AA41" s="52"/>
@@ -58191,7 +58197,7 @@
     </row>
     <row r="42" spans="1:30">
       <c r="A42" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B42">
         <v>4</v>
@@ -58265,10 +58271,10 @@
         <v>349.57984645161292</v>
       </c>
       <c r="X42" s="36" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="Y42" s="36" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="Z42" s="35"/>
       <c r="AA42" s="35"/>
@@ -58278,7 +58284,7 @@
     </row>
     <row r="43" spans="1:30">
       <c r="A43" s="14" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B43">
         <v>5</v>
@@ -58314,10 +58320,10 @@
         <v>#DIV/0!</v>
       </c>
       <c r="X43" s="36" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="Y43" s="36" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Z43" s="35"/>
       <c r="AA43" s="35"/>
@@ -58327,7 +58333,7 @@
     </row>
     <row r="44" spans="1:30">
       <c r="A44" s="4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B44">
         <v>5</v>
@@ -58363,10 +58369,10 @@
         <v>#DIV/0!</v>
       </c>
       <c r="X44" s="36" t="s">
+        <v>494</v>
+      </c>
+      <c r="Y44" s="36" t="s">
         <v>495</v>
-      </c>
-      <c r="Y44" s="36" t="s">
-        <v>496</v>
       </c>
       <c r="Z44" s="35"/>
       <c r="AA44" s="35"/>
@@ -60701,7 +60707,7 @@
       <c r="L107" s="2"/>
       <c r="M107" s="2"/>
       <c r="O107" s="2" t="e">
-        <f t="shared" ref="O107:O138" si="8">60/N107</f>
+        <f t="shared" ref="O107:O123" si="8">60/N107</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U107" s="2"/>
@@ -61441,7 +61447,7 @@
         <v>76</v>
       </c>
       <c r="J1" s="91" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="K1" s="91"/>
       <c r="L1" s="91"/>
@@ -61544,10 +61550,10 @@
         <v>196</v>
       </c>
       <c r="X3" s="17" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Y3" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="Z3" t="s">
         <v>281</v>
@@ -61641,10 +61647,10 @@
         <v>265.88181119999996</v>
       </c>
       <c r="X4" s="36" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="Y4" s="36" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="Z4" s="52"/>
       <c r="AA4" s="52"/>
@@ -61728,10 +61734,10 @@
         <v>257.93387042817682</v>
       </c>
       <c r="X5" s="36" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="Y5" s="36" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="Z5" s="52"/>
       <c r="AA5" s="52"/>
@@ -61815,10 +61821,10 @@
         <v>230.17156302729532</v>
       </c>
       <c r="X6" s="36" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Y6" s="36" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="Z6" s="35"/>
       <c r="AA6" s="35"/>
@@ -61902,10 +61908,10 @@
         <v>260.56283616000002</v>
       </c>
       <c r="X7" s="36" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Y7" s="36" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Z7" s="35"/>
       <c r="AA7" s="35"/>
@@ -61989,10 +61995,10 @@
         <v>228.55816285714283</v>
       </c>
       <c r="X8" s="36" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="Y8" s="36" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="Z8" s="35"/>
       <c r="AA8" s="35"/>
@@ -62076,10 +62082,10 @@
         <v>227.70789103124994</v>
       </c>
       <c r="X9" s="36" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Y9" s="36" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="Z9" s="35"/>
       <c r="AA9" s="35"/>
@@ -62163,10 +62169,10 @@
         <v>224.32301239436623</v>
       </c>
       <c r="X10" s="36" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Y10" s="36" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="Z10" s="52"/>
       <c r="AA10" s="52"/>
@@ -62176,7 +62182,7 @@
     </row>
     <row r="11" spans="1:30">
       <c r="A11" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B11" s="4">
         <v>4</v>
@@ -62250,10 +62256,10 @@
         <v>254.60580959999999</v>
       </c>
       <c r="X11" s="36" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Y11" s="36" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Z11" s="52"/>
       <c r="AA11" s="52"/>
@@ -62263,7 +62269,7 @@
     </row>
     <row r="12" spans="1:30">
       <c r="A12" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B12" s="4">
         <v>4</v>
@@ -62337,10 +62343,10 @@
         <v>250.31141694915254</v>
       </c>
       <c r="X12" s="89" t="s">
+        <v>501</v>
+      </c>
+      <c r="Y12" s="36" t="s">
         <v>502</v>
-      </c>
-      <c r="Y12" s="36" t="s">
-        <v>503</v>
       </c>
       <c r="Z12" s="52"/>
       <c r="AA12" s="52"/>
@@ -66567,7 +66573,7 @@
         <v>239</v>
       </c>
       <c r="M1" s="91" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="N1" s="91"/>
       <c r="O1" s="91"/>
@@ -66669,10 +66675,10 @@
         <v>196</v>
       </c>
       <c r="X3" s="17" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Y3" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -66751,10 +66757,10 @@
         <v>541.0704366315789</v>
       </c>
       <c r="X4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="Y4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -66833,10 +66839,10 @@
         <v>523.80355619117631</v>
       </c>
       <c r="X5" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="Y5" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -66915,10 +66921,10 @@
         <v>523.61121595744669</v>
       </c>
       <c r="X6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="Y6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -66996,10 +67002,10 @@
         <v>530</v>
       </c>
       <c r="X7" t="s">
+        <v>394</v>
+      </c>
+      <c r="Y7" t="s">
         <v>395</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -67078,10 +67084,10 @@
         <v>511.20297234042556</v>
       </c>
       <c r="X8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="Y8" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -67160,10 +67166,10 @@
         <v>569.5418090322579</v>
       </c>
       <c r="X9" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Y9" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -67242,10 +67248,10 @@
         <v>455.43647706122442</v>
       </c>
       <c r="X10" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="Y10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -67324,10 +67330,10 @@
         <v>534.45251666666661</v>
       </c>
       <c r="X11" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="Y11" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -67406,10 +67412,10 @@
         <v>490.437296590909</v>
       </c>
       <c r="X12" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="Y12" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -67488,10 +67494,10 @@
         <v>551.20784154639171</v>
       </c>
       <c r="X13" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="Y13" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -67570,10 +67576,10 @@
         <v>637.65872047058815</v>
       </c>
       <c r="X14" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Y14" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -67652,10 +67658,10 @@
         <v>543.19706999999994</v>
       </c>
       <c r="X15" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="Y15" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -67724,7 +67730,7 @@
         <v>120</v>
       </c>
       <c r="U16">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="V16" t="s">
         <v>87</v>
@@ -67734,15 +67740,15 @@
         <v>600.68470524999998</v>
       </c>
       <c r="X16" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Y16" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="17" spans="1:25" s="4" customFormat="1">
       <c r="A17" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B17" s="4">
         <v>4</v>
@@ -67806,7 +67812,7 @@
         <v>120</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="V17" t="s">
         <v>87</v>
@@ -67816,15 +67822,15 @@
         <v>591.63690253846141</v>
       </c>
       <c r="X17" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="Y17" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="18" spans="1:25" s="72" customFormat="1">
       <c r="A18" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B18">
         <v>4</v>
@@ -67898,10 +67904,10 @@
         <v>575.17852431818187</v>
       </c>
       <c r="X18" t="s">
+        <v>504</v>
+      </c>
+      <c r="Y18" t="s">
         <v>505</v>
-      </c>
-      <c r="Y18" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -68587,7 +68593,7 @@
         <v>66</v>
       </c>
       <c r="K1" s="91" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="L1" s="91"/>
       <c r="M1" s="91"/>
@@ -68689,10 +68695,10 @@
         <v>196</v>
       </c>
       <c r="X3" s="17" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Y3" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:25" s="72" customFormat="1">
@@ -69539,7 +69545,7 @@
         <v>74</v>
       </c>
       <c r="K1" s="91" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="L1" s="91"/>
       <c r="M1" s="91"/>
@@ -69647,10 +69653,10 @@
         <v>196</v>
       </c>
       <c r="X3" s="17" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Y3" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -69730,10 +69736,10 @@
         <v>641.47553883870955</v>
       </c>
       <c r="X4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="Y4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -69813,10 +69819,10 @@
         <v>469.21067715789474</v>
       </c>
       <c r="X5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="Y5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -69896,10 +69902,10 @@
         <v>504.70727999999997</v>
       </c>
       <c r="X6" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="Y6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -69979,10 +69985,10 @@
         <v>504.80263693280637</v>
       </c>
       <c r="X7" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="Y7" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -70062,10 +70068,10 @@
         <v>396.20211110653582</v>
       </c>
       <c r="X8" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Y8" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -70145,10 +70151,10 @@
         <v>636.95264523287653</v>
       </c>
       <c r="X9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="Y9" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -70228,10 +70234,10 @@
         <v>467.041615458904</v>
       </c>
       <c r="X10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="Y10" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="11" spans="1:25" s="72" customFormat="1">
@@ -70311,15 +70317,15 @@
         <v>510.41361253012042</v>
       </c>
       <c r="X11" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="Y11" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="12" spans="1:25" s="72" customFormat="1">
       <c r="A12" t="s">
-        <v>329</v>
+        <v>521</v>
       </c>
       <c r="B12">
         <v>4</v>
@@ -70394,15 +70400,15 @@
         <v>529.21317600000009</v>
       </c>
       <c r="X12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="Y12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="13" spans="1:25">
       <c r="A13" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B13">
         <v>4</v>
@@ -70464,7 +70470,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="T13">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U13">
         <v>6.6</v>
@@ -70477,15 +70483,15 @@
         <v>497.13965018181813</v>
       </c>
       <c r="X13" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Y13" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="14" spans="1:25">
       <c r="A14" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B14">
         <v>5</v>
@@ -70515,10 +70521,10 @@
         <v>#DIV/0!</v>
       </c>
       <c r="X14" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="Y14" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="15" spans="1:25">
